--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128556551</v>
+        <v>128556233</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>91906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490719</v>
+        <v>490748</v>
       </c>
       <c r="R2" t="n">
-        <v>6725697</v>
+        <v>6725682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128556233</v>
+        <v>128556551</v>
       </c>
       <c r="B3" t="n">
-        <v>91906</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490748</v>
+        <v>490719</v>
       </c>
       <c r="R3" t="n">
-        <v>6725682</v>
+        <v>6725697</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128557963</v>
+        <v>128555456</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490797</v>
+        <v>490795</v>
       </c>
       <c r="R5" t="n">
-        <v>6725875</v>
+        <v>6725680</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128555456</v>
+        <v>128557963</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490795</v>
+        <v>490797</v>
       </c>
       <c r="R6" t="n">
-        <v>6725680</v>
+        <v>6725875</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128556233</v>
       </c>
       <c r="B2" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128556551</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128555563</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128555456</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128557963</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128556662</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128555333</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128554899</v>
       </c>
       <c r="B9" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128556288</v>
       </c>
       <c r="B10" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128555247</v>
       </c>
       <c r="B11" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128555151</v>
+        <v>128555132</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,34 +1770,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490760</v>
+        <v>490774</v>
       </c>
       <c r="R12" t="n">
-        <v>6725743</v>
+        <v>6725729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1844,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128555132</v>
+        <v>128555151</v>
       </c>
       <c r="B13" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,39 +1887,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490774</v>
+        <v>490760</v>
       </c>
       <c r="R13" t="n">
-        <v>6725729</v>
+        <v>6725743</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,12 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,7 +1986,7 @@
         <v>128557151</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>128557272</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>128555010</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128558137</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>128556938</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>128555192</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128556728</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128556365</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128556233</v>
+        <v>128556551</v>
       </c>
       <c r="B2" t="n">
-        <v>91912</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490748</v>
+        <v>490719</v>
       </c>
       <c r="R2" t="n">
-        <v>6725682</v>
+        <v>6725697</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128556551</v>
+        <v>128556233</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>91918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490719</v>
+        <v>490748</v>
       </c>
       <c r="R3" t="n">
-        <v>6725697</v>
+        <v>6725682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1437,7 +1437,7 @@
         <v>128554899</v>
       </c>
       <c r="B9" t="n">
-        <v>92766</v>
+        <v>92772</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128556288</v>
       </c>
       <c r="B10" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128555247</v>
       </c>
       <c r="B11" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128555132</v>
+        <v>128555151</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,39 +1770,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490774</v>
+        <v>490760</v>
       </c>
       <c r="R12" t="n">
-        <v>6725729</v>
+        <v>6725743</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,12 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128555151</v>
+        <v>128555132</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,34 +1877,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490760</v>
+        <v>490774</v>
       </c>
       <c r="R13" t="n">
-        <v>6725743</v>
+        <v>6725729</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1951,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128557151</v>
+        <v>128557272</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,34 +1994,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490763</v>
+        <v>490761</v>
       </c>
       <c r="R14" t="n">
-        <v>6725792</v>
+        <v>6725787</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2068,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128557272</v>
+        <v>128557151</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,39 +2111,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490761</v>
+        <v>490763</v>
       </c>
       <c r="R15" t="n">
-        <v>6725787</v>
+        <v>6725792</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,12 +2180,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128555010</v>
+        <v>128556938</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,24 +2218,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2245,7 +2250,7 @@
         <v>490773</v>
       </c>
       <c r="R16" t="n">
-        <v>6725776</v>
+        <v>6725780</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,12 +2292,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Draperad tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,10 +2324,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128558137</v>
+        <v>128555192</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2335,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490788</v>
+        <v>490774</v>
       </c>
       <c r="R17" t="n">
-        <v>6725884</v>
+        <v>6725717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2399,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,12 +2409,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128556938</v>
+        <v>128555010</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,29 +2452,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2474,7 +2479,7 @@
         <v>490773</v>
       </c>
       <c r="R18" t="n">
-        <v>6725780</v>
+        <v>6725776</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,7 +2511,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2516,12 +2521,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128555192</v>
+        <v>128558137</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,39 +2564,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490774</v>
+        <v>490788</v>
       </c>
       <c r="R19" t="n">
-        <v>6725717</v>
+        <v>6725884</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128556551</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128556233</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128555563</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128555456</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128555333</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128554899</v>
       </c>
       <c r="B9" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128556288</v>
       </c>
       <c r="B10" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128555247</v>
       </c>
       <c r="B11" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128555151</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128557272</v>
+        <v>128557151</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,39 +1994,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490761</v>
+        <v>490763</v>
       </c>
       <c r="R14" t="n">
-        <v>6725787</v>
+        <v>6725792</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,12 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128557151</v>
+        <v>128557272</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,34 +2101,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490763</v>
+        <v>490761</v>
       </c>
       <c r="R15" t="n">
-        <v>6725792</v>
+        <v>6725787</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,7 +2175,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128556938</v>
+        <v>128555010</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,29 +2218,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2250,7 +2245,7 @@
         <v>490773</v>
       </c>
       <c r="R16" t="n">
-        <v>6725780</v>
+        <v>6725776</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,12 +2287,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2324,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128555192</v>
+        <v>128558137</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,39 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490774</v>
+        <v>490788</v>
       </c>
       <c r="R17" t="n">
-        <v>6725717</v>
+        <v>6725884</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2409,12 +2399,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128555010</v>
+        <v>128556938</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,24 +2442,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2479,7 +2474,7 @@
         <v>490773</v>
       </c>
       <c r="R18" t="n">
-        <v>6725776</v>
+        <v>6725780</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2506,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2521,12 +2516,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Draperad tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128558137</v>
+        <v>128555192</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,34 +2559,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490788</v>
+        <v>490774</v>
       </c>
       <c r="R19" t="n">
-        <v>6725884</v>
+        <v>6725717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,7 +2668,7 @@
         <v>128556728</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128556365</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128556551</v>
+        <v>128556233</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490719</v>
+        <v>490748</v>
       </c>
       <c r="R2" t="n">
-        <v>6725697</v>
+        <v>6725682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128556233</v>
+        <v>128556551</v>
       </c>
       <c r="B3" t="n">
-        <v>91920</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490748</v>
+        <v>490719</v>
       </c>
       <c r="R3" t="n">
-        <v>6725682</v>
+        <v>6725697</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128556233</v>
       </c>
       <c r="B2" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128554899</v>
       </c>
       <c r="B9" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128556288</v>
       </c>
       <c r="B10" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128555247</v>
       </c>
       <c r="B11" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128556233</v>
+        <v>128556551</v>
       </c>
       <c r="B2" t="n">
-        <v>91921</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490748</v>
+        <v>490719</v>
       </c>
       <c r="R2" t="n">
-        <v>6725682</v>
+        <v>6725697</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128556551</v>
+        <v>128556233</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>91948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490719</v>
+        <v>490748</v>
       </c>
       <c r="R3" t="n">
-        <v>6725697</v>
+        <v>6725682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>128555563</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128555456</v>
+        <v>128557963</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490795</v>
+        <v>490797</v>
       </c>
       <c r="R5" t="n">
-        <v>6725680</v>
+        <v>6725875</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128557963</v>
+        <v>128555456</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490797</v>
+        <v>490795</v>
       </c>
       <c r="R6" t="n">
-        <v>6725875</v>
+        <v>6725680</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,7 +1218,7 @@
         <v>128556662</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128555333</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128554899</v>
       </c>
       <c r="B9" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128556288</v>
       </c>
       <c r="B10" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128555247</v>
       </c>
       <c r="B11" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128555151</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>128555132</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128557151</v>
+        <v>128557272</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,34 +1994,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490763</v>
+        <v>490761</v>
       </c>
       <c r="R14" t="n">
-        <v>6725792</v>
+        <v>6725787</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2068,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128557272</v>
+        <v>128557151</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,39 +2111,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490761</v>
+        <v>490763</v>
       </c>
       <c r="R15" t="n">
-        <v>6725787</v>
+        <v>6725792</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,12 +2180,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,7 +2210,7 @@
         <v>128555010</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128558137</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>128556938</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>128555192</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128556728</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128556365</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128557963</v>
+        <v>128555456</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490797</v>
+        <v>490795</v>
       </c>
       <c r="R5" t="n">
-        <v>6725875</v>
+        <v>6725680</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128555456</v>
+        <v>128557963</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490795</v>
+        <v>490797</v>
       </c>
       <c r="R6" t="n">
-        <v>6725680</v>
+        <v>6725875</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128557272</v>
+        <v>128557151</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,39 +1994,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490761</v>
+        <v>490763</v>
       </c>
       <c r="R14" t="n">
-        <v>6725787</v>
+        <v>6725792</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,12 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128557151</v>
+        <v>128557272</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,34 +2101,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490763</v>
+        <v>490761</v>
       </c>
       <c r="R15" t="n">
-        <v>6725792</v>
+        <v>6725787</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,7 +2175,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128556551</v>
+        <v>128556233</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>91953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490719</v>
+        <v>490748</v>
       </c>
       <c r="R2" t="n">
-        <v>6725697</v>
+        <v>6725682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128556233</v>
+        <v>128556551</v>
       </c>
       <c r="B3" t="n">
-        <v>91948</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490748</v>
+        <v>490719</v>
       </c>
       <c r="R3" t="n">
-        <v>6725682</v>
+        <v>6725697</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>128555563</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128555456</v>
+        <v>128557963</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490795</v>
+        <v>490797</v>
       </c>
       <c r="R5" t="n">
-        <v>6725680</v>
+        <v>6725875</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128557963</v>
+        <v>128555456</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490797</v>
+        <v>490795</v>
       </c>
       <c r="R6" t="n">
-        <v>6725875</v>
+        <v>6725680</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,7 +1330,7 @@
         <v>128555333</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128554899</v>
       </c>
       <c r="B9" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128556288</v>
       </c>
       <c r="B10" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128555247</v>
       </c>
       <c r="B11" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128555151</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128557151</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128555010</v>
+        <v>128556938</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,24 +2218,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2245,7 +2250,7 @@
         <v>490773</v>
       </c>
       <c r="R16" t="n">
-        <v>6725776</v>
+        <v>6725780</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,12 +2292,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Draperad tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,10 +2324,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128558137</v>
+        <v>128555192</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2335,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490788</v>
+        <v>490774</v>
       </c>
       <c r="R17" t="n">
-        <v>6725884</v>
+        <v>6725717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2399,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,12 +2409,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128556938</v>
+        <v>128555010</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,29 +2452,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2474,7 +2479,7 @@
         <v>490773</v>
       </c>
       <c r="R18" t="n">
-        <v>6725780</v>
+        <v>6725776</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,7 +2511,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2516,12 +2521,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128555192</v>
+        <v>128558137</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,39 +2564,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490774</v>
+        <v>490788</v>
       </c>
       <c r="R19" t="n">
-        <v>6725717</v>
+        <v>6725884</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,7 +2668,7 @@
         <v>128556728</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128556365</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128556233</v>
+        <v>128556551</v>
       </c>
       <c r="B2" t="n">
-        <v>91953</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490748</v>
+        <v>490719</v>
       </c>
       <c r="R2" t="n">
-        <v>6725682</v>
+        <v>6725697</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128556551</v>
+        <v>128556233</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>91958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490719</v>
+        <v>490748</v>
       </c>
       <c r="R3" t="n">
-        <v>6725697</v>
+        <v>6725682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1437,7 +1437,7 @@
         <v>128554899</v>
       </c>
       <c r="B9" t="n">
-        <v>92807</v>
+        <v>92812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128556288</v>
       </c>
       <c r="B10" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128555247</v>
       </c>
       <c r="B11" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128555151</v>
+        <v>128555132</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,34 +1770,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490760</v>
+        <v>490774</v>
       </c>
       <c r="R12" t="n">
-        <v>6725743</v>
+        <v>6725729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1844,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128555132</v>
+        <v>128555151</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,39 +1887,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490774</v>
+        <v>490760</v>
       </c>
       <c r="R13" t="n">
-        <v>6725729</v>
+        <v>6725743</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,12 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128556938</v>
+        <v>128555010</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,29 +2218,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2250,7 +2245,7 @@
         <v>490773</v>
       </c>
       <c r="R16" t="n">
-        <v>6725780</v>
+        <v>6725776</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,12 +2287,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2324,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128555192</v>
+        <v>128558137</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,39 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490774</v>
+        <v>490788</v>
       </c>
       <c r="R17" t="n">
-        <v>6725717</v>
+        <v>6725884</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2409,12 +2399,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128555010</v>
+        <v>128556938</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,24 +2442,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2479,7 +2474,7 @@
         <v>490773</v>
       </c>
       <c r="R18" t="n">
-        <v>6725776</v>
+        <v>6725780</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2506,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2521,12 +2516,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Draperad tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128558137</v>
+        <v>128555192</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,34 +2559,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490788</v>
+        <v>490774</v>
       </c>
       <c r="R19" t="n">
-        <v>6725884</v>
+        <v>6725717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128556551</v>
+        <v>128556233</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>91958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490719</v>
+        <v>490748</v>
       </c>
       <c r="R2" t="n">
-        <v>6725697</v>
+        <v>6725682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128556233</v>
+        <v>128556551</v>
       </c>
       <c r="B3" t="n">
-        <v>91958</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490748</v>
+        <v>490719</v>
       </c>
       <c r="R3" t="n">
-        <v>6725682</v>
+        <v>6725697</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128557963</v>
+        <v>128555456</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490797</v>
+        <v>490795</v>
       </c>
       <c r="R5" t="n">
-        <v>6725875</v>
+        <v>6725680</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128555456</v>
+        <v>128557963</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490795</v>
+        <v>490797</v>
       </c>
       <c r="R6" t="n">
-        <v>6725680</v>
+        <v>6725875</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128555132</v>
+        <v>128555151</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,39 +1770,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490774</v>
+        <v>490760</v>
       </c>
       <c r="R12" t="n">
-        <v>6725729</v>
+        <v>6725743</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,12 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128555151</v>
+        <v>128555132</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,34 +1877,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490760</v>
+        <v>490774</v>
       </c>
       <c r="R13" t="n">
-        <v>6725743</v>
+        <v>6725729</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1951,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128555010</v>
+        <v>128556938</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,24 +2218,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2245,7 +2250,7 @@
         <v>490773</v>
       </c>
       <c r="R16" t="n">
-        <v>6725776</v>
+        <v>6725780</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,12 +2292,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Draperad tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,10 +2324,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128558137</v>
+        <v>128555192</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2335,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490788</v>
+        <v>490774</v>
       </c>
       <c r="R17" t="n">
-        <v>6725884</v>
+        <v>6725717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2399,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,12 +2409,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128556938</v>
+        <v>128555010</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,29 +2452,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2474,7 +2479,7 @@
         <v>490773</v>
       </c>
       <c r="R18" t="n">
-        <v>6725780</v>
+        <v>6725776</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,7 +2511,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2516,12 +2521,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128555192</v>
+        <v>128558137</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,39 +2564,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490774</v>
+        <v>490788</v>
       </c>
       <c r="R19" t="n">
-        <v>6725717</v>
+        <v>6725884</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128556938</v>
+        <v>128555010</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,29 +2218,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2250,7 +2245,7 @@
         <v>490773</v>
       </c>
       <c r="R16" t="n">
-        <v>6725780</v>
+        <v>6725776</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,12 +2287,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2324,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128555192</v>
+        <v>128558137</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,39 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490774</v>
+        <v>490788</v>
       </c>
       <c r="R17" t="n">
-        <v>6725717</v>
+        <v>6725884</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2409,12 +2399,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128555010</v>
+        <v>128556938</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,24 +2442,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2479,7 +2474,7 @@
         <v>490773</v>
       </c>
       <c r="R18" t="n">
-        <v>6725776</v>
+        <v>6725780</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2506,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2521,12 +2516,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Draperad tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128558137</v>
+        <v>128555192</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,34 +2559,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490788</v>
+        <v>490774</v>
       </c>
       <c r="R19" t="n">
-        <v>6725884</v>
+        <v>6725717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128556233</v>
       </c>
       <c r="B2" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128556551</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128555563</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128555456</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128557963</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128556662</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128555333</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128554899</v>
       </c>
       <c r="B9" t="n">
-        <v>92812</v>
+        <v>92816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128556288</v>
       </c>
       <c r="B10" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128555247</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128555151</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>128555132</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128557151</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>128557272</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>128555010</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128558137</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>128556938</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>128555192</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128556728</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128556365</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128555151</v>
+        <v>128555132</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,34 +1770,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490760</v>
+        <v>490774</v>
       </c>
       <c r="R12" t="n">
-        <v>6725743</v>
+        <v>6725729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1844,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128555132</v>
+        <v>128555151</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,39 +1887,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490774</v>
+        <v>490760</v>
       </c>
       <c r="R13" t="n">
-        <v>6725729</v>
+        <v>6725743</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,12 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128557151</v>
+        <v>128557272</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,34 +1994,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490763</v>
+        <v>490761</v>
       </c>
       <c r="R14" t="n">
-        <v>6725792</v>
+        <v>6725787</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2068,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128557272</v>
+        <v>128557151</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,39 +2111,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490761</v>
+        <v>490763</v>
       </c>
       <c r="R15" t="n">
-        <v>6725787</v>
+        <v>6725792</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,12 +2180,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128555010</v>
+        <v>128556938</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,24 +2218,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2245,7 +2250,7 @@
         <v>490773</v>
       </c>
       <c r="R16" t="n">
-        <v>6725776</v>
+        <v>6725780</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,12 +2292,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Draperad tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,10 +2324,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128558137</v>
+        <v>128555192</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2335,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490788</v>
+        <v>490774</v>
       </c>
       <c r="R17" t="n">
-        <v>6725884</v>
+        <v>6725717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,7 +2399,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2399,12 +2409,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128556938</v>
+        <v>128555010</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,29 +2452,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2474,7 +2479,7 @@
         <v>490773</v>
       </c>
       <c r="R18" t="n">
-        <v>6725780</v>
+        <v>6725776</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,7 +2511,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2516,12 +2521,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128555192</v>
+        <v>128558137</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,39 +2564,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490774</v>
+        <v>490788</v>
       </c>
       <c r="R19" t="n">
-        <v>6725717</v>
+        <v>6725884</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128555132</v>
+        <v>128555151</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,39 +1770,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490774</v>
+        <v>490760</v>
       </c>
       <c r="R12" t="n">
-        <v>6725729</v>
+        <v>6725743</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,12 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128555151</v>
+        <v>128555132</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,34 +1877,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490760</v>
+        <v>490774</v>
       </c>
       <c r="R13" t="n">
-        <v>6725743</v>
+        <v>6725729</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1951,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128557272</v>
+        <v>128557151</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,39 +1994,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490761</v>
+        <v>490763</v>
       </c>
       <c r="R14" t="n">
-        <v>6725787</v>
+        <v>6725792</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,12 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128557151</v>
+        <v>128557272</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,34 +2101,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490763</v>
+        <v>490761</v>
       </c>
       <c r="R15" t="n">
-        <v>6725792</v>
+        <v>6725787</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,7 +2175,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,7 +2207,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128556938</v>
+        <v>128555192</v>
       </c>
       <c r="B16" t="n">
         <v>57720</v>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490773</v>
+        <v>490774</v>
       </c>
       <c r="R16" t="n">
-        <v>6725780</v>
+        <v>6725717</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2324,7 +2324,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128555192</v>
+        <v>128556938</v>
       </c>
       <c r="B17" t="n">
         <v>57720</v>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490774</v>
+        <v>490773</v>
       </c>
       <c r="R17" t="n">
-        <v>6725717</v>
+        <v>6725780</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128556233</v>
       </c>
       <c r="B2" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128556551</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128555563</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128555456</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128557963</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128556662</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128555333</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128554899</v>
       </c>
       <c r="B9" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128556288</v>
       </c>
       <c r="B10" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128555247</v>
       </c>
       <c r="B11" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128555151</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>128555132</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128557151</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>128557272</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128555192</v>
+        <v>128555010</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,39 +2218,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490774</v>
+        <v>490773</v>
       </c>
       <c r="R16" t="n">
-        <v>6725717</v>
+        <v>6725776</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,12 +2287,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2324,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128556938</v>
+        <v>128558137</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,39 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490773</v>
+        <v>490788</v>
       </c>
       <c r="R17" t="n">
-        <v>6725780</v>
+        <v>6725884</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2409,12 +2399,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128555010</v>
+        <v>128556938</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,24 +2442,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2479,7 +2474,7 @@
         <v>490773</v>
       </c>
       <c r="R18" t="n">
-        <v>6725776</v>
+        <v>6725780</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2506,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2521,12 +2516,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Draperad tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128558137</v>
+        <v>128555192</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,34 +2559,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490788</v>
+        <v>490774</v>
       </c>
       <c r="R19" t="n">
-        <v>6725884</v>
+        <v>6725717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,7 +2668,7 @@
         <v>128556728</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128556365</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128556233</v>
+        <v>128556551</v>
       </c>
       <c r="B2" t="n">
-        <v>91970</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490748</v>
+        <v>490719</v>
       </c>
       <c r="R2" t="n">
-        <v>6725682</v>
+        <v>6725697</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128556551</v>
+        <v>128556233</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>91975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490719</v>
+        <v>490748</v>
       </c>
       <c r="R3" t="n">
-        <v>6725697</v>
+        <v>6725682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>128555563</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128555456</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128555333</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128554899</v>
       </c>
       <c r="B9" t="n">
-        <v>92824</v>
+        <v>92829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128556288</v>
       </c>
       <c r="B10" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128555247</v>
       </c>
       <c r="B11" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128555132</v>
+        <v>128555151</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,39 +1770,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490774</v>
+        <v>490760</v>
       </c>
       <c r="R12" t="n">
-        <v>6725729</v>
+        <v>6725743</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,12 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128555151</v>
+        <v>128555132</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,34 +1877,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490760</v>
+        <v>490774</v>
       </c>
       <c r="R13" t="n">
-        <v>6725743</v>
+        <v>6725729</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1951,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,7 +1986,7 @@
         <v>128557151</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128556938</v>
+        <v>128555010</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,29 +2218,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2250,7 +2245,7 @@
         <v>490773</v>
       </c>
       <c r="R16" t="n">
-        <v>6725780</v>
+        <v>6725776</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,12 +2287,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2324,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128555192</v>
+        <v>128558137</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,39 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490774</v>
+        <v>490788</v>
       </c>
       <c r="R17" t="n">
-        <v>6725717</v>
+        <v>6725884</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2409,12 +2399,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128555010</v>
+        <v>128556938</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,24 +2442,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
@@ -2479,7 +2474,7 @@
         <v>490773</v>
       </c>
       <c r="R18" t="n">
-        <v>6725776</v>
+        <v>6725780</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2506,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2521,12 +2516,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Draperad tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128558137</v>
+        <v>128555192</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,34 +2559,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490788</v>
+        <v>490774</v>
       </c>
       <c r="R19" t="n">
-        <v>6725884</v>
+        <v>6725717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,7 +2668,7 @@
         <v>128556728</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128556365</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128556551</v>
+        <v>128556233</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>91975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490719</v>
+        <v>490748</v>
       </c>
       <c r="R2" t="n">
-        <v>6725697</v>
+        <v>6725682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128556233</v>
+        <v>128556551</v>
       </c>
       <c r="B3" t="n">
-        <v>91975</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490748</v>
+        <v>490719</v>
       </c>
       <c r="R3" t="n">
-        <v>6725682</v>
+        <v>6725697</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128556233</v>
+        <v>128556551</v>
       </c>
       <c r="B2" t="n">
-        <v>91975</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490748</v>
+        <v>490719</v>
       </c>
       <c r="R2" t="n">
-        <v>6725682</v>
+        <v>6725697</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128556551</v>
+        <v>128556233</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>91981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490719</v>
+        <v>490748</v>
       </c>
       <c r="R3" t="n">
-        <v>6725697</v>
+        <v>6725682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>128555563</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128555456</v>
+        <v>128557963</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490795</v>
+        <v>490797</v>
       </c>
       <c r="R5" t="n">
-        <v>6725680</v>
+        <v>6725875</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128557963</v>
+        <v>128555456</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490797</v>
+        <v>490795</v>
       </c>
       <c r="R6" t="n">
-        <v>6725875</v>
+        <v>6725680</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,7 +1330,7 @@
         <v>128555333</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128554899</v>
       </c>
       <c r="B9" t="n">
-        <v>92829</v>
+        <v>92837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128556288</v>
       </c>
       <c r="B10" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128555247</v>
       </c>
       <c r="B11" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128555151</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128557151</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>128555010</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>128558137</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>128556728</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>128556365</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128556551</v>
+        <v>128555247</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490719</v>
+        <v>490782</v>
       </c>
       <c r="R2" t="n">
-        <v>6725697</v>
+        <v>6725717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128556233</v>
+        <v>128556288</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490748</v>
+        <v>490746</v>
       </c>
       <c r="R3" t="n">
-        <v>6725682</v>
+        <v>6725694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128555563</v>
+        <v>128556233</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490792</v>
+        <v>490748</v>
       </c>
       <c r="R4" t="n">
-        <v>6725651</v>
+        <v>6725682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128557963</v>
+        <v>128554899</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>93215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4368</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490797</v>
+        <v>490791</v>
       </c>
       <c r="R5" t="n">
-        <v>6725875</v>
+        <v>6725807</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1069,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,12 +1079,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,6 +1088,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,14 +1107,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128555456</v>
+        <v>128555010</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490795</v>
+        <v>490773</v>
       </c>
       <c r="R6" t="n">
-        <v>6725680</v>
+        <v>6725776</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1187,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,32 +1219,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128556662</v>
+        <v>128555151</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490758</v>
+        <v>490760</v>
       </c>
       <c r="R7" t="n">
-        <v>6725732</v>
+        <v>6725743</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,12 +1299,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,11 +1329,11 @@
         <v>128555333</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1434,48 +1433,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128554899</v>
+        <v>128555456</v>
       </c>
       <c r="B9" t="n">
-        <v>92837</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490791</v>
+        <v>490795</v>
       </c>
       <c r="R9" t="n">
-        <v>6725807</v>
+        <v>6725680</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1522,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1545,32 +1540,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128556288</v>
+        <v>128555563</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490746</v>
+        <v>490792</v>
       </c>
       <c r="R10" t="n">
-        <v>6725694</v>
+        <v>6725651</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1620,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,32 +1647,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128555247</v>
+        <v>128555619</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490782</v>
+        <v>490781</v>
       </c>
       <c r="R11" t="n">
-        <v>6725717</v>
+        <v>6725634</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1732,7 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,14 +1754,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128555151</v>
+        <v>128555935</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1794,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490760</v>
+        <v>490756</v>
       </c>
       <c r="R12" t="n">
-        <v>6725743</v>
+        <v>6725643</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,50 +1861,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128555132</v>
+        <v>128556365</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490774</v>
+        <v>490746</v>
       </c>
       <c r="R13" t="n">
-        <v>6725729</v>
+        <v>6725693</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,12 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,14 +1968,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128557151</v>
+        <v>128556551</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2018,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490763</v>
+        <v>490719</v>
       </c>
       <c r="R14" t="n">
-        <v>6725792</v>
+        <v>6725697</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,50 +2075,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128557272</v>
+        <v>128556728</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490761</v>
+        <v>490758</v>
       </c>
       <c r="R15" t="n">
-        <v>6725787</v>
+        <v>6725757</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,12 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,14 +2182,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128555010</v>
+        <v>128557151</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2242,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490773</v>
+        <v>490763</v>
       </c>
       <c r="R16" t="n">
-        <v>6725776</v>
+        <v>6725792</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2287,12 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Draperad tall.</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,11 +2292,11 @@
         <v>128558137</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2431,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128556938</v>
+        <v>128555132</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490773</v>
+        <v>490774</v>
       </c>
       <c r="R18" t="n">
-        <v>6725780</v>
+        <v>6725729</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2516,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2551,7 +2521,7 @@
         <v>128555192</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128556728</v>
+        <v>128555991</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,34 +2646,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490758</v>
+        <v>490746</v>
       </c>
       <c r="R20" t="n">
-        <v>6725757</v>
+        <v>6725657</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2735,7 +2710,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2745,7 +2720,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2772,10 +2752,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128556365</v>
+        <v>128556085</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2783,34 +2763,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörkån, Mörkån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490746</v>
+        <v>490745</v>
       </c>
       <c r="R21" t="n">
-        <v>6725693</v>
+        <v>6725669</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2842,7 +2827,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2852,7 +2837,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,6 +2866,585 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128556662</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mörkån, Mörkån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>490758</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6725732</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128556938</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mörkån, Mörkån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>490773</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6725780</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128557272</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mörkån, Mörkån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>490761</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6725787</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128557963</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mörkån, Mörkån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>490797</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6725875</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128554664</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mörkån, Mörkån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>490824</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6725892</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40636-2025 artfynd.xlsx
+++ b/artfynd/A 40636-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555247</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556288</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556233</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128554899</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555010</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555151</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1430,6 +1465,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555333</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555456</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555563</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555619</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555935</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1965,6 +2025,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556365</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2072,6 +2137,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556551</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,6 +2249,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556728</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2286,6 +2361,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128557151</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2398,6 +2478,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128558137</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2515,6 +2600,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555132</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2632,6 +2722,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555192</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2749,6 +2844,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128555991</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2866,6 +2966,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556085</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2978,6 +3083,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556662</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3095,6 +3205,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128556938</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3212,6 +3327,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128557272</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3324,6 +3444,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128557963</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3445,8 +3570,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128554664</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>